--- a/projetos_completos.xlsx
+++ b/projetos_completos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://planaltopr-my.sharepoint.com/personal/carlos_ramos_presidencia_gov_br/Documents/Área de Trabalho/Painel-Projetos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_23518B7812FC80020B993711595ED87656C74E4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ACAFA2E-C110-4974-BBD0-2B3DAB88B5BC}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_23518B7812FC80020B993711595ED87656C74E4B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B37C2E34-9A15-4B59-8936-4351306F2A8E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1245" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projetos Completos" sheetId="1" r:id="rId1"/>
@@ -5489,11 +5489,11 @@
     <col min="20" max="20" width="50" customWidth="1"/>
     <col min="21" max="22" width="18" customWidth="1"/>
     <col min="23" max="23" width="50" customWidth="1"/>
-    <col min="24" max="24" width="16" customWidth="1"/>
+    <col min="24" max="24" width="21.5703125" customWidth="1"/>
     <col min="25" max="25" width="7" customWidth="1"/>
     <col min="26" max="26" width="16" customWidth="1"/>
     <col min="27" max="27" width="18" customWidth="1"/>
-    <col min="28" max="28" width="8" customWidth="1"/>
+    <col min="28" max="28" width="22.140625" customWidth="1"/>
     <col min="29" max="29" width="27" customWidth="1"/>
     <col min="30" max="30" width="50" customWidth="1"/>
     <col min="31" max="31" width="20" customWidth="1"/>
